--- a/public/planilhas/03_painel_okr_habitos.xlsx
+++ b/public/planilhas/03_painel_okr_habitos.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HABITOS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$R$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,12 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0;(#,##0);&quot;—&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;(#,##0.0);&quot;—&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,6 +120,37 @@
       <color rgb="00D9534F"/>
       <sz val="18"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="00C99C66"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -168,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -205,10 +238,26 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="16" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="19" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -220,12 +269,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="0043D07F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="00D9534F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Aptos Narrow"/>
@@ -484,6 +548,219 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Gap até a meta</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!C25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$26:$B$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$C$26:$C$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!D25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E9E5B"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$26:$B$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$D$26:$D$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!E25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="D9534F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$26:$B$28</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$E$26:$E$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!C35</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="15000">
+              <a:solidFill>
+                <a:srgbClr val="C99C66"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$36:$B$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$C$36:$C$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -525,6 +802,50 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3960000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3960000" cy="1440000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -822,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:Z50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -944,27 +1265,27 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="7">
-        <f>B40</f>
+        <f>Z40</f>
         <v/>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="8">
-        <f>B41</f>
+        <f>Z41</f>
         <v/>
       </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="9">
-        <f>B42</f>
+        <f>Z42</f>
         <v/>
       </c>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="10">
-        <f>B43</f>
+        <f>Z43</f>
         <v/>
       </c>
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="11">
-        <f>B44</f>
+        <f>Z44</f>
         <v/>
       </c>
       <c r="K6" s="6" t="n"/>
@@ -1222,7 +1543,11 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Cascata · gap dos top 4 OKRs</t>
+        </is>
+      </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
@@ -1233,62 +1558,287 @@
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
-    </row>
-    <row r="25">
+      <c r="N24" s="14" t="inlineStr">
+        <is>
+          <t>MINI-SPARKLINES</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Etapa</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
+      <c r="N25" s="15" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="inlineStr">
+        <is>
+          <t>Atual</t>
+        </is>
+      </c>
+      <c r="P25" s="15" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="Q25" s="15" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="R25" s="15" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="S25" s="15" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="T25" s="15" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="U25" s="15" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="V25" s="15" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Meta total</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="17">
+        <f>IF(G26&gt;=0,G26,0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="17">
+        <f>IF(G26&lt;0,-G26,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="17">
+        <f>G26</f>
+        <v/>
+      </c>
+      <c r="G26" s="18">
+        <f>SUM(OKRS!C6:C9)</f>
+        <v/>
+      </c>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Progresso %</t>
+        </is>
+      </c>
+      <c r="O26" s="20">
+        <f>$Z$40*100</f>
+        <v/>
+      </c>
+      <c r="P26" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q26" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="R26" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="S26" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="T26" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="U26" s="21">
+        <f>$Z$40*100</f>
+        <v/>
+      </c>
+      <c r="V26" s="22">
+        <f>IF(P26=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((P26-(MIN(P26:U26)))/MAX(1E-9,(MAX(P26:U26))-(MIN(P26:U26)))*7+1,0))),1))&amp;IF(Q26=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((Q26-(MIN(P26:U26)))/MAX(1E-9,(MAX(P26:U26))-(MIN(P26:U26)))*7+1,0))),1))&amp;IF(R26=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((R26-(MIN(P26:U26)))/MAX(1E-9,(MAX(P26:U26))-(MIN(P26:U26)))*7+1,0))),1))&amp;IF(S26=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((S26-(MIN(P26:U26)))/MAX(1E-9,(MAX(P26:U26))-(MIN(P26:U26)))*7+1,0))),1))&amp;IF(T26=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((T26-(MIN(P26:U26)))/MAX(1E-9,(MAX(P26:U26))-(MIN(P26:U26)))*7+1,0))),1))&amp;IF(U26=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((U26-(MIN(P26:U26)))/MAX(1E-9,(MAX(P26:U26))-(MIN(P26:U26)))*7+1,0))),1))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>− Já feito</t>
+        </is>
+      </c>
+      <c r="C27" s="17">
+        <f>IF(G27&gt;=0,F26,F26+G27)</f>
+        <v/>
+      </c>
+      <c r="D27" s="17">
+        <f>IF(G27&gt;=0,G27,0)</f>
+        <v/>
+      </c>
+      <c r="E27" s="17">
+        <f>IF(G27&lt;0,-G27,0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="17">
+        <f>F26+G27</f>
+        <v/>
+      </c>
+      <c r="G27" s="18">
+        <f>-SUM(OKRS!D6:D9)</f>
+        <v/>
+      </c>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>No ritmo</t>
+        </is>
+      </c>
+      <c r="O27" s="20">
+        <f>$Z$41</f>
+        <v/>
+      </c>
+      <c r="P27" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S27" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" s="21">
+        <f>$Z$41</f>
+        <v/>
+      </c>
+      <c r="V27" s="22">
+        <f>IF(P27=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((P27-(MIN(P27:U27)))/MAX(1E-9,(MAX(P27:U27))-(MIN(P27:U27)))*7+1,0))),1))&amp;IF(Q27=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((Q27-(MIN(P27:U27)))/MAX(1E-9,(MAX(P27:U27))-(MIN(P27:U27)))*7+1,0))),1))&amp;IF(R27=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((R27-(MIN(P27:U27)))/MAX(1E-9,(MAX(P27:U27))-(MIN(P27:U27)))*7+1,0))),1))&amp;IF(S27=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((S27-(MIN(P27:U27)))/MAX(1E-9,(MAX(P27:U27))-(MIN(P27:U27)))*7+1,0))),1))&amp;IF(T27=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((T27-(MIN(P27:U27)))/MAX(1E-9,(MAX(P27:U27))-(MIN(P27:U27)))*7+1,0))),1))&amp;IF(U27=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((U27-(MIN(P27:U27)))/MAX(1E-9,(MAX(P27:U27))-(MIN(P27:U27)))*7+1,0))),1))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Gap restante</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="17">
+        <f>IF(G28&gt;=0,G28,0)</f>
+        <v/>
+      </c>
+      <c r="E28" s="17">
+        <f>IF(G28&lt;0,-G28,0)</f>
+        <v/>
+      </c>
+      <c r="F28" s="17">
+        <f>G28</f>
+        <v/>
+      </c>
+      <c r="G28" s="18">
+        <f>SUM(OKRS!C6:C9)-SUM(OKRS!D6:D9)</f>
+        <v/>
+      </c>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Hábitos %</t>
+        </is>
+      </c>
+      <c r="O28" s="20">
+        <f>$Z$43*100</f>
+        <v/>
+      </c>
+      <c r="P28" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q28" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="R28" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="S28" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="T28" s="21" t="n">
+        <v>65</v>
+      </c>
+      <c r="U28" s="21">
+        <f>$Z$43*100</f>
+        <v/>
+      </c>
+      <c r="V28" s="22">
+        <f>IF(P28=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((P28-(MIN(P28:U28)))/MAX(1E-9,(MAX(P28:U28))-(MIN(P28:U28)))*7+1,0))),1))&amp;IF(Q28=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((Q28-(MIN(P28:U28)))/MAX(1E-9,(MAX(P28:U28))-(MIN(P28:U28)))*7+1,0))),1))&amp;IF(R28=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((R28-(MIN(P28:U28)))/MAX(1E-9,(MAX(P28:U28))-(MIN(P28:U28)))*7+1,0))),1))&amp;IF(S28=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((S28-(MIN(P28:U28)))/MAX(1E-9,(MAX(P28:U28))-(MIN(P28:U28)))*7+1,0))),1))&amp;IF(T28=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((T28-(MIN(P28:U28)))/MAX(1E-9,(MAX(P28:U28))-(MIN(P28:U28)))*7+1,0))),1))&amp;IF(U28=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((U28-(MIN(P28:U28)))/MAX(1E-9,(MAX(P28:U28))-(MIN(P28:U28)))*7+1,0))),1))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -1362,7 +1912,11 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Spark · progresso por OKR</t>
+        </is>
+      </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
@@ -1374,11 +1928,23 @@
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Ponto</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
@@ -1390,9 +1956,19 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>OKR1</t>
+        </is>
+      </c>
+      <c r="C36" s="25">
+        <f>OKRS!E6*100</f>
+        <v/>
+      </c>
+      <c r="D36" s="26">
+        <f>IF(OR(C36="",NOT(ISNUMBER(C36))),"",REPT("▬",MAX(1,ROUND((C36-(MIN(C36:C41)))/MAX(1E-9,(MAX(C36:C41))-(MIN(C36:C41)))*10,0))))</f>
+        <v/>
+      </c>
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
@@ -1404,9 +1980,19 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>OKR2</t>
+        </is>
+      </c>
+      <c r="C37" s="25">
+        <f>OKRS!E7*100</f>
+        <v/>
+      </c>
+      <c r="D37" s="26">
+        <f>IF(OR(C37="",NOT(ISNUMBER(C37))),"",REPT("▬",MAX(1,ROUND((C37-(MIN(C36:C41)))/MAX(1E-9,(MAX(C36:C41))-(MIN(C36:C41)))*10,0))))</f>
+        <v/>
+      </c>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
@@ -1418,9 +2004,19 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>OKR3</t>
+        </is>
+      </c>
+      <c r="C38" s="25">
+        <f>OKRS!E8*100</f>
+        <v/>
+      </c>
+      <c r="D38" s="26">
+        <f>IF(OR(C38="",NOT(ISNUMBER(C38))),"",REPT("▬",MAX(1,ROUND((C38-(MIN(C36:C41)))/MAX(1E-9,(MAX(C36:C41))-(MIN(C36:C41)))*10,0))))</f>
+        <v/>
+      </c>
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
@@ -1432,9 +2028,19 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>OKR4</t>
+        </is>
+      </c>
+      <c r="C39" s="25">
+        <f>OKRS!E9*100</f>
+        <v/>
+      </c>
+      <c r="D39" s="26">
+        <f>IF(OR(C39="",NOT(ISNUMBER(C39))),"",REPT("▬",MAX(1,ROUND((C39-(MIN(C36:C41)))/MAX(1E-9,(MAX(C36:C41))-(MIN(C36:C41)))*10,0))))</f>
+        <v/>
+      </c>
       <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
@@ -1446,12 +2052,19 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="14">
-        <f>AVERAGE(OKRS!E6:E11)</f>
-        <v/>
-      </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>OKR5</t>
+        </is>
+      </c>
+      <c r="C40" s="25">
+        <f>OKRS!E10*100</f>
+        <v/>
+      </c>
+      <c r="D40" s="26">
+        <f>IF(OR(C40="",NOT(ISNUMBER(C40))),"",REPT("▬",MAX(1,ROUND((C40-(MIN(C36:C41)))/MAX(1E-9,(MAX(C36:C41))-(MIN(C36:C41)))*10,0))))</f>
+        <v/>
+      </c>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
@@ -1460,15 +2073,26 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
+      <c r="Z40" s="27">
+        <f>AVERAGE(OKRS!E6:E11)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="14">
-        <f>COUNTIF(OKRS!H6:H11,"🟢 no ritmo")</f>
-        <v/>
-      </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>OKR6</t>
+        </is>
+      </c>
+      <c r="C41" s="25">
+        <f>OKRS!E11*100</f>
+        <v/>
+      </c>
+      <c r="D41" s="26">
+        <f>IF(OR(C41="",NOT(ISNUMBER(C41))),"",REPT("▬",MAX(1,ROUND((C41-(MIN(C36:C41)))/MAX(1E-9,(MAX(C36:C41))-(MIN(C36:C41)))*10,0))))</f>
+        <v/>
+      </c>
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
@@ -1477,13 +2101,14 @@
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
+      <c r="Z41" s="27">
+        <f>COUNTIF(OKRS!H6:H11,"🟢 no ritmo")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="14">
-        <f>COUNTIF(OKRS!H6:H11,"🔴 fora do ritmo")</f>
-        <v/>
-      </c>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
@@ -1494,13 +2119,14 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
+      <c r="Z42" s="27">
+        <f>COUNTIF(OKRS!H6:H11,"🔴 fora do ritmo")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
-      <c r="B43" s="14">
-        <f>AVERAGE(HABITOS!I6:I11)</f>
-        <v/>
-      </c>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
@@ -1511,13 +2137,14 @@
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
+      <c r="Z43" s="27">
+        <f>AVERAGE(HABITOS!I6:I11)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
-      <c r="B44" s="14">
-        <f>COUNTA(OKRS!A6:A11)</f>
-        <v/>
-      </c>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
@@ -1528,6 +2155,10 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
+      <c r="Z44" s="27">
+        <f>COUNTA(OKRS!A6:A11)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1634,6 +2265,23 @@
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="F7:G7"/>
   </mergeCells>
+  <conditionalFormatting sqref="G26:G28">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O26:O28">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00C99C66"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1764,32 +2412,32 @@
       <c r="J5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Faturar R$ 40k/mês</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="29" t="n">
         <v>12000</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="28" t="n">
         <v>40000</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="30" t="n">
         <v>26500</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="31">
         <f>IFERROR((D6-B6)/(C6-B6),0)</f>
         <v/>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="32" t="n">
         <v>46375</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="33">
         <f>IFERROR((D6-B6)/40,0)</f>
         <v/>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="34">
         <f>IF((D6+G6*(F6-TODAY()))&gt;=C6,"🟢 no ritmo",IF((D6+G6*(F6-TODAY()))&gt;=C6*0.8,"🟡 risco","🔴 fora do ritmo"))</f>
         <v/>
       </c>
@@ -1797,32 +2445,32 @@
       <c r="J6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Reserva de emergência</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="28" t="n">
         <v>30000</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="30" t="n">
         <v>14500</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="31">
         <f>IFERROR((D7-B7)/(C7-B7),0)</f>
         <v/>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="32" t="n">
         <v>46345</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="33">
         <f>IFERROR((D7-B7)/40,0)</f>
         <v/>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="34">
         <f>IF((D7+G7*(F7-TODAY()))&gt;=C7,"🟢 no ritmo",IF((D7+G7*(F7-TODAY()))&gt;=C7*0.8,"🟡 risco","🔴 fora do ritmo"))</f>
         <v/>
       </c>
@@ -1830,32 +2478,32 @@
       <c r="J7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Reduzir custo fixo</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="29" t="n">
         <v>8000</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="28" t="n">
         <v>5000</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="30" t="n">
         <v>6800</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="31">
         <f>IFERROR((D8-B8)/(C8-B8),0)</f>
         <v/>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="32" t="n">
         <v>46315</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="33">
         <f>IFERROR((D8-B8)/40,0)</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="34">
         <f>IF((D8+G8*(F8-TODAY()))&gt;=C8,"🟢 no ritmo",IF((D8+G8*(F8-TODAY()))&gt;=C8*0.8,"🟡 risco","🔴 fora do ritmo"))</f>
         <v/>
       </c>
@@ -1863,32 +2511,32 @@
       <c r="J8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Fechar 12 contratos</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="31">
         <f>IFERROR((D9-B9)/(C9-B9),0)</f>
         <v/>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="32" t="n">
         <v>46385</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="33">
         <f>IFERROR((D9-B9)/40,0)</f>
         <v/>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="34">
         <f>IF((D9+G9*(F9-TODAY()))&gt;=C9,"🟢 no ritmo",IF((D9+G9*(F9-TODAY()))&gt;=C9*0.8,"🟡 risco","🔴 fora do ritmo"))</f>
         <v/>
       </c>
@@ -1896,32 +2544,32 @@
       <c r="J9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>MRR de produto</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="28" t="n">
         <v>15000</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="30" t="n">
         <v>6200</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="31">
         <f>IFERROR((D10-B10)/(C10-B10),0)</f>
         <v/>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="32" t="n">
         <v>46425</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="33">
         <f>IFERROR((D10-B10)/40,0)</f>
         <v/>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="34">
         <f>IF((D10+G10*(F10-TODAY()))&gt;=C10,"🟢 no ritmo",IF((D10+G10*(F10-TODAY()))&gt;=C10*0.8,"🟡 risco","🔴 fora do ritmo"))</f>
         <v/>
       </c>
@@ -1929,32 +2577,32 @@
       <c r="J10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>NPS acima de 70</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="28" t="n">
         <v>70</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="31">
         <f>IFERROR((D11-B11)/(C11-B11),0)</f>
         <v/>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="32" t="n">
         <v>46305</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="33">
         <f>IFERROR((D11-B11)/40,0)</f>
         <v/>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="34">
         <f>IF((D11+G11*(F11-TODAY()))&gt;=C11,"🟢 no ritmo",IF((D11+G11*(F11-TODAY()))&gt;=C11*0.8,"🟡 risco","🔴 fora do ritmo"))</f>
         <v/>
       </c>
@@ -2565,7 +3213,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H11">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
       <formula>"🔴 fora do ritmo"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2727,33 +3375,33 @@
       <c r="N5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Treino / movimento</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="n">
+      <c r="D6" s="35" t="n"/>
+      <c r="E6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="23" t="n">
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="36">
         <f>COUNTIF(B6:H6,1)/7</f>
         <v/>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="16">
         <f>IF(I6&gt;=0.8,"🔥 forte",IF(I6&gt;=0.5,"ok","⚠ frágil"))</f>
         <v/>
       </c>
@@ -2763,33 +3411,33 @@
       <c r="N6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Leitura 20min</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="23" t="n"/>
-      <c r="D7" s="23" t="n">
+      <c r="C7" s="35" t="n"/>
+      <c r="D7" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="23" t="n"/>
-      <c r="G7" s="23" t="n">
+      <c r="F7" s="35" t="n"/>
+      <c r="G7" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="23" t="n">
+      <c r="H7" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="36">
         <f>COUNTIF(B7:H7,1)/7</f>
         <v/>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="16">
         <f>IF(I7&gt;=0.8,"🔥 forte",IF(I7&gt;=0.5,"ok","⚠ frágil"))</f>
         <v/>
       </c>
@@ -2799,31 +3447,31 @@
       <c r="N7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Prospecção comercial</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D8" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="23" t="n"/>
-      <c r="F8" s="23" t="n">
+      <c r="E8" s="35" t="n"/>
+      <c r="F8" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="23" t="n"/>
-      <c r="H8" s="23" t="n"/>
-      <c r="I8" s="24">
+      <c r="G8" s="35" t="n"/>
+      <c r="H8" s="35" t="n"/>
+      <c r="I8" s="36">
         <f>COUNTIF(B8:H8,1)/7</f>
         <v/>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="16">
         <f>IF(I8&gt;=0.8,"🔥 forte",IF(I8&gt;=0.5,"ok","⚠ frágil"))</f>
         <v/>
       </c>
@@ -2833,35 +3481,35 @@
       <c r="N8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Registrar finanças</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="23" t="n"/>
-      <c r="I9" s="24">
+      <c r="H9" s="35" t="n"/>
+      <c r="I9" s="36">
         <f>COUNTIF(B9:H9,1)/7</f>
         <v/>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="16">
         <f>IF(I9&gt;=0.8,"🔥 forte",IF(I9&gt;=0.5,"ok","⚠ frágil"))</f>
         <v/>
       </c>
@@ -2871,33 +3519,33 @@
       <c r="N9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Sono 7h+</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n">
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n">
+      <c r="E10" s="35" t="n"/>
+      <c r="F10" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="36">
         <f>COUNTIF(B10:H10,1)/7</f>
         <v/>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="16">
         <f>IF(I10&gt;=0.8,"🔥 forte",IF(I10&gt;=0.5,"ok","⚠ frágil"))</f>
         <v/>
       </c>
@@ -2907,31 +3555,31 @@
       <c r="N10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Deep work 2h</t>
         </is>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n">
+      <c r="D11" s="35" t="n"/>
+      <c r="E11" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="23" t="n"/>
-      <c r="H11" s="23" t="n"/>
-      <c r="I11" s="24">
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="35" t="n"/>
+      <c r="I11" s="36">
         <f>COUNTIF(B11:H11,1)/7</f>
         <v/>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="16">
         <f>IF(I11&gt;=0.8,"🔥 forte",IF(I11&gt;=0.5,"ok","⚠ frágil"))</f>
         <v/>
       </c>
